--- a/data/trans_camb/P0901-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,09</t>
+          <t>1,28; 7,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,19</t>
+          <t>1,57; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 10,42</t>
+          <t>3,81; 10,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,28</t>
+          <t>4,95; 13,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,16</t>
+          <t>6,98; 15,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,87</t>
+          <t>4,72; 11,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,79</t>
+          <t>4,56; 9,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,34</t>
+          <t>5,43; 10,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,11</t>
+          <t>5,14; 9,9</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 120,46</t>
+          <t>12,41; 114,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 119,25</t>
+          <t>15,42; 120,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,0; 149,63</t>
+          <t>39,08; 154,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 123,44</t>
+          <t>33,2; 120,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,15; 139,03</t>
+          <t>47,64; 139,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 99,76</t>
+          <t>32,07; 108,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,25; 107,05</t>
+          <t>40,07; 108,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,16; 110,0</t>
+          <t>47,31; 114,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,91; 109,07</t>
+          <t>44,22; 109,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,84</t>
+          <t>-0,26; 5,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,89</t>
+          <t>-2,7; 2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 3,64</t>
+          <t>-6,21; 3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,93</t>
+          <t>2,85; 10,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,4</t>
+          <t>-1,5; 5,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,36</t>
+          <t>1,08; 7,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,96</t>
+          <t>2,37; 7,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,24</t>
+          <t>-1,09; 3,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,2</t>
+          <t>-3,91; 4,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 70,11</t>
+          <t>-2,68; 67,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 35,3</t>
+          <t>-23,71; 33,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 38,69</t>
+          <t>-55,23; 40,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 69,59</t>
+          <t>16,01; 68,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 37,33</t>
+          <t>-8,87; 38,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 52,03</t>
+          <t>5,8; 52,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 57,78</t>
+          <t>16,48; 62,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 27,79</t>
+          <t>-7,82; 28,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 33,78</t>
+          <t>-26,38; 33,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,38</t>
+          <t>-1,79; 4,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,98</t>
+          <t>-3,08; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,09</t>
+          <t>3,0; 9,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,79</t>
+          <t>-2,85; 4,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,05</t>
+          <t>-2,86; 5,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 2,45</t>
+          <t>-11,39; 2,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,47</t>
+          <t>-1,45; 3,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,8</t>
+          <t>-2,16; 2,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 5,12</t>
+          <t>-3,24; 5,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 62,41</t>
+          <t>-18,91; 60,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 40,98</t>
+          <t>-30,95; 40,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,16; 144,64</t>
+          <t>26,12; 136,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 30,24</t>
+          <t>-15,04; 32,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 32,65</t>
+          <t>-14,8; 32,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 14,44</t>
+          <t>-58,85; 14,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 29,53</t>
+          <t>-10,39; 31,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 24,14</t>
+          <t>-15,25; 25,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 41,07</t>
+          <t>-22,48; 41,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,19</t>
+          <t>0,27; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,4</t>
+          <t>-1,15; 4,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,63</t>
+          <t>2,1; 7,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,77</t>
+          <t>-1,34; 5,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,52</t>
+          <t>-2,29; 4,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,98</t>
+          <t>-2,02; 6,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,72</t>
+          <t>0,32; 4,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,5</t>
+          <t>-1,21; 3,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,3</t>
+          <t>1,33; 6,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 74,03</t>
+          <t>2,66; 77,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 54,53</t>
+          <t>-10,81; 57,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,48; 97,18</t>
+          <t>20,27; 97,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 35,61</t>
+          <t>-7,29; 33,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 26,1</t>
+          <t>-11,96; 25,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 36,25</t>
+          <t>-9,91; 39,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 37,31</t>
+          <t>2,24; 36,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 26,84</t>
+          <t>-7,45; 25,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,81; 48,86</t>
+          <t>9,23; 50,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,52</t>
+          <t>1,47; 4,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,86</t>
+          <t>0,07; 2,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,79</t>
+          <t>0,73; 5,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,41</t>
+          <t>2,56; 6,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,05</t>
+          <t>1,35; 4,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,78</t>
+          <t>-0,78; 4,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,92</t>
+          <t>2,54; 5,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,48</t>
+          <t>1,17; 3,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,74</t>
+          <t>1,03; 4,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,92; 53,7</t>
+          <t>14,95; 54,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 33,58</t>
+          <t>0,64; 35,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12,55; 67,29</t>
+          <t>8,15; 66,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,62; 41,1</t>
+          <t>14,64; 42,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,47; 32,48</t>
+          <t>7,75; 32,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 30,37</t>
+          <t>-3,93; 31,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,96; 40,72</t>
+          <t>19,02; 41,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,88; 28,49</t>
+          <t>8,63; 29,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,7; 39,08</t>
+          <t>8,1; 40,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0901-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>7,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,92</t>
+          <t>1,54; 7,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,19</t>
+          <t>1,59; 8,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,31</t>
+          <t>3,39; 10,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,25</t>
+          <t>5,27; 13,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 15,15</t>
+          <t>6,92; 15,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,64</t>
+          <t>4,41; 11,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,73</t>
+          <t>4,66; 9,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,66</t>
+          <t>5,1; 10,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,9</t>
+          <t>4,97; 9,92</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 114,21</t>
+          <t>13,53; 110,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 120,58</t>
+          <t>15,03; 113,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,08; 154,53</t>
+          <t>34,75; 146,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,2; 120,13</t>
+          <t>36,91; 120,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,64; 139,66</t>
+          <t>46,37; 136,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,07; 108,83</t>
+          <t>29,81; 101,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,07; 108,89</t>
+          <t>40,22; 105,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,31; 114,28</t>
+          <t>43,76; 114,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,22; 109,15</t>
+          <t>41,89; 108,35</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>3,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,56</t>
+          <t>-0,04; 5,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,88</t>
+          <t>-2,42; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,57</t>
+          <t>-0,86; 5,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,0</t>
+          <t>2,74; 10,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,5</t>
+          <t>-1,85; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,77</t>
+          <t>1,07; 7,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,25</t>
+          <t>2,15; 6,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,24</t>
+          <t>-1,41; 3,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 4,13</t>
+          <t>1,01; 5,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,39%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 67,1</t>
+          <t>-0,22; 70,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 33,53</t>
+          <t>-21,97; 36,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,23; 40,16</t>
+          <t>-8,27; 60,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 68,63</t>
+          <t>15,05; 69,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 38,58</t>
+          <t>-10,12; 37,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 52,79</t>
+          <t>6,49; 52,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,48; 62,05</t>
+          <t>14,7; 58,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 28,48</t>
+          <t>-9,9; 27,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 33,74</t>
+          <t>7,73; 46,06</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,36</t>
+          <t>-2,05; 4,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,81</t>
+          <t>-3,34; 2,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,96</t>
+          <t>2,44; 9,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,96</t>
+          <t>-3,31; 4,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,06</t>
+          <t>-2,73; 5,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 2,58</t>
+          <t>-1,63; 5,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,85</t>
+          <t>-1,62; 3,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,99</t>
+          <t>-2,19; 3,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,12</t>
+          <t>1,6; 6,48</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-16,22%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 60,89</t>
+          <t>-20,57; 59,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 40,43</t>
+          <t>-32,9; 39,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,12; 136,94</t>
+          <t>20,35; 128,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 32,3</t>
+          <t>-16,99; 30,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 32,68</t>
+          <t>-13,95; 33,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,85; 14,88</t>
+          <t>-8,25; 37,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 31,71</t>
+          <t>-11,28; 28,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 25,47</t>
+          <t>-15,06; 26,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 41,05</t>
+          <t>10,4; 55,06</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>4,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,33</t>
+          <t>0,31; 6,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,56</t>
+          <t>-0,95; 4,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,74</t>
+          <t>1,78; 7,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,65</t>
+          <t>-1,23; 5,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,38</t>
+          <t>-2,72; 4,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,42</t>
+          <t>0,4; 7,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,75</t>
+          <t>0,22; 4,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,23</t>
+          <t>-1,0; 3,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,25</t>
+          <t>2,13; 6,39</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 77,81</t>
+          <t>2,04; 77,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 57,07</t>
+          <t>-9,82; 55,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,27; 97,78</t>
+          <t>17,32; 95,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 33,6</t>
+          <t>-6,37; 33,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 25,81</t>
+          <t>-13,86; 27,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 39,03</t>
+          <t>1,97; 43,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 36,45</t>
+          <t>1,08; 37,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 25,68</t>
+          <t>-6,65; 27,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 50,43</t>
+          <t>14,25; 51,1</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>4,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,54</t>
+          <t>1,37; 4,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,92</t>
+          <t>-0,08; 2,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,68</t>
+          <t>3,03; 6,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,58</t>
+          <t>2,51; 6,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,99</t>
+          <t>1,22; 5,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,92</t>
+          <t>2,65; 6,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,06</t>
+          <t>2,44; 4,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,6</t>
+          <t>1,16; 3,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,95</t>
+          <t>3,41; 5,75</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,95; 54,47</t>
+          <t>14,52; 54,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,64; 35,0</t>
+          <t>-0,97; 35,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,15; 66,62</t>
+          <t>31,09; 73,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,64; 42,34</t>
+          <t>14,46; 42,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,75; 32,4</t>
+          <t>6,97; 32,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 31,54</t>
+          <t>15,5; 39,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,02; 41,64</t>
+          <t>18,39; 40,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,63; 29,42</t>
+          <t>8,71; 28,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8,1; 40,04</t>
+          <t>25,65; 47,89</t>
         </is>
       </c>
     </row>
